--- a/submissions/lianafarsi/cleaned_dataset_lianafarsi.xlsx
+++ b/submissions/lianafarsi/cleaned_dataset_lianafarsi.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:R61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,6 +518,11 @@
           <t>satisfaction_score</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>data_quality_issue</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -587,6 +592,11 @@
       <c r="Q2" t="n">
         <v>5</v>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -656,6 +666,11 @@
       <c r="Q3" t="n">
         <v>3</v>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -725,6 +740,11 @@
       <c r="Q4" t="n">
         <v>1</v>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -794,6 +814,11 @@
       <c r="Q5" t="n">
         <v>4</v>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -863,6 +888,11 @@
       <c r="Q6" t="n">
         <v>4</v>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -932,6 +962,11 @@
       <c r="Q7" t="n">
         <v>2</v>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1001,6 +1036,11 @@
       <c r="Q8" t="n">
         <v>5</v>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1070,6 +1110,11 @@
       <c r="Q9" t="n">
         <v>1</v>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1139,6 +1184,11 @@
       <c r="Q10" t="n">
         <v>2</v>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1155,7 +1205,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>145</v>
+        <v>45</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1207,6 +1257,11 @@
       </c>
       <c r="Q11" t="n">
         <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1277,6 +1332,11 @@
       <c r="Q12" t="n">
         <v>2</v>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1346,6 +1406,11 @@
       <c r="Q13" t="n">
         <v>2</v>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1415,6 +1480,11 @@
       <c r="Q14" t="n">
         <v>5</v>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1484,6 +1554,11 @@
       <c r="Q15" t="n">
         <v>4</v>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1553,6 +1628,11 @@
       <c r="Q16" t="n">
         <v>4</v>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1622,6 +1702,11 @@
       <c r="Q17" t="n">
         <v>2</v>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1691,6 +1776,11 @@
       <c r="Q18" t="n">
         <v>4</v>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1760,6 +1850,11 @@
       <c r="Q19" t="n">
         <v>1</v>
       </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1829,6 +1924,11 @@
       <c r="Q20" t="n">
         <v>2</v>
       </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1845,7 +1945,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45.2</v>
+        <v>45</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1897,6 +1997,11 @@
       </c>
       <c r="Q21" t="n">
         <v>5</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1967,6 +2072,11 @@
       <c r="Q22" t="n">
         <v>1</v>
       </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2036,6 +2146,11 @@
       <c r="Q23" t="n">
         <v>2</v>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2105,6 +2220,11 @@
       <c r="Q24" t="n">
         <v>4</v>
       </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2174,6 +2294,11 @@
       <c r="Q25" t="n">
         <v>1</v>
       </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2243,6 +2368,11 @@
       <c r="Q26" t="n">
         <v>2</v>
       </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2312,6 +2442,11 @@
       <c r="Q27" t="n">
         <v>4</v>
       </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2381,6 +2516,11 @@
       <c r="Q28" t="n">
         <v>3</v>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2450,6 +2590,11 @@
       <c r="Q29" t="n">
         <v>5</v>
       </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2519,6 +2664,11 @@
       <c r="Q30" t="n">
         <v>5</v>
       </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2562,7 +2712,7 @@
         <v>156.89</v>
       </c>
       <c r="K31" t="n">
-        <v>25000</v>
+        <v>4079.139999999999</v>
       </c>
       <c r="L31" t="n">
         <v>340</v>
@@ -2587,6 +2737,11 @@
       </c>
       <c r="Q31" t="n">
         <v>4</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2657,6 +2812,11 @@
       <c r="Q32" t="n">
         <v>3</v>
       </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2726,6 +2886,11 @@
       <c r="Q33" t="n">
         <v>5</v>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2769,7 +2934,7 @@
         <v>230.05</v>
       </c>
       <c r="K34" t="n">
-        <v>5521.2</v>
+        <v>5521.200000000001</v>
       </c>
       <c r="L34" t="n">
         <v>112</v>
@@ -2794,6 +2959,11 @@
       </c>
       <c r="Q34" t="n">
         <v>5</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -2864,6 +3034,11 @@
       <c r="Q35" t="n">
         <v>3</v>
       </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2933,6 +3108,11 @@
       <c r="Q36" t="n">
         <v>3</v>
       </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3002,6 +3182,11 @@
       <c r="Q37" t="n">
         <v>2</v>
       </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3071,6 +3256,11 @@
       <c r="Q38" t="n">
         <v>2</v>
       </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3140,6 +3330,11 @@
       <c r="Q39" t="n">
         <v>4</v>
       </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3209,6 +3404,11 @@
       <c r="Q40" t="n">
         <v>4</v>
       </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3252,7 +3452,7 @@
         <v>37.66</v>
       </c>
       <c r="K41" t="n">
-        <v>3749.667333333333</v>
+        <v>1280.44</v>
       </c>
       <c r="L41" t="n">
         <v>126</v>
@@ -3277,6 +3477,11 @@
       </c>
       <c r="Q41" t="n">
         <v>2</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -3347,6 +3552,11 @@
       <c r="Q42" t="n">
         <v>5</v>
       </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3416,6 +3626,11 @@
       <c r="Q43" t="n">
         <v>5</v>
       </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3485,6 +3700,11 @@
       <c r="Q44" t="n">
         <v>4</v>
       </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3554,6 +3774,11 @@
       <c r="Q45" t="n">
         <v>2</v>
       </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3623,6 +3848,11 @@
       <c r="Q46" t="n">
         <v>1</v>
       </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3666,7 +3896,7 @@
         <v>328.23</v>
       </c>
       <c r="K47" t="n">
-        <v>4923.45</v>
+        <v>4923.450000000001</v>
       </c>
       <c r="L47" t="n">
         <v>229</v>
@@ -3691,6 +3921,11 @@
       </c>
       <c r="Q47" t="n">
         <v>4</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -3761,6 +3996,11 @@
       <c r="Q48" t="n">
         <v>3</v>
       </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3830,6 +4070,11 @@
       <c r="Q49" t="n">
         <v>2</v>
       </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3899,6 +4144,11 @@
       <c r="Q50" t="n">
         <v>1</v>
       </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3968,6 +4218,11 @@
       <c r="Q51" t="n">
         <v>2</v>
       </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4037,6 +4292,11 @@
       <c r="Q52" t="n">
         <v>5</v>
       </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4106,6 +4366,11 @@
       <c r="Q53" t="n">
         <v>3</v>
       </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4149,7 +4414,7 @@
         <v>322.53</v>
       </c>
       <c r="K54" t="n">
-        <v>5805.54</v>
+        <v>5805.539999999999</v>
       </c>
       <c r="L54" t="n">
         <v>320</v>
@@ -4174,6 +4439,11 @@
       </c>
       <c r="Q54" t="n">
         <v>1</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -4244,6 +4514,11 @@
       <c r="Q55" t="n">
         <v>1</v>
       </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4313,6 +4588,11 @@
       <c r="Q56" t="n">
         <v>1</v>
       </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4382,6 +4662,11 @@
       <c r="Q57" t="n">
         <v>2</v>
       </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4451,6 +4736,11 @@
       <c r="Q58" t="n">
         <v>4</v>
       </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4520,6 +4810,11 @@
       <c r="Q59" t="n">
         <v>2</v>
       </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4563,7 +4858,7 @@
         <v>287.05</v>
       </c>
       <c r="K60" t="n">
-        <v>8898.549999999999</v>
+        <v>8898.550000000001</v>
       </c>
       <c r="L60" t="n">
         <v>224</v>
@@ -4588,6 +4883,11 @@
       </c>
       <c r="Q60" t="n">
         <v>5</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -4657,6 +4957,11 @@
       </c>
       <c r="Q61" t="n">
         <v>3</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
   </sheetData>
